--- a/data/trans_orig/IP22B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22B-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8809</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14589</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15156</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>24927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>13709</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23749</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,32%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>15744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26151</t>
+          <t>25971</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17079</t>
+          <t>17050</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>24269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24077</t>
+          <t>24485</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18180</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28860</t>
+          <t>28674</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>34806</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49046</t>
+          <t>49500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,84%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>25167</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26172</t>
+          <t>26789</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>34194</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49211</t>
+          <t>49438</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,77%</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,05%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>15836</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>22541</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>23368</t>
+          <t>23216</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32388</t>
+          <t>32576</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4482,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16220</t>
+          <t>15945</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>55,95%</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>10529</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>44990</t>
+          <t>45233</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>63052</t>
+          <t>62880</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>50873</t>
+          <t>50974</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>69563</t>
+          <t>70120</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>101875</t>
+          <t>101153</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>127105</t>
+          <t>127834</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>55207</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>74508</t>
+          <t>73723</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>71365</t>
+          <t>70989</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>90465</t>
+          <t>90696</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>131777</t>
+          <t>133193</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>158013</t>
+          <t>159708</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,78%</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>21338</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15394</t>
+          <t>15737</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29411</t>
+          <t>29331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>11934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>21328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,68%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20911</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23801</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34563</t>
+          <t>34469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,71%</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22606</t>
+          <t>22482</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36021</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45335</t>
+          <t>44851</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63496</t>
+          <t>62752</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>38757</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28427</t>
+          <t>28403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41468</t>
+          <t>42137</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>58276</t>
+          <t>58398</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76832</t>
+          <t>76759</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>30890</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>29820</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>43937</t>
+          <t>44037</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,86%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13919</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22509</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21535</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>26811</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>41174</t>
+          <t>41515</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>541</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>14922</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9889</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>52611</t>
+          <t>53974</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>73187</t>
+          <t>73620</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>73421</t>
+          <t>72835</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>96970</t>
+          <t>95362</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>132092</t>
+          <t>132995</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>163191</t>
+          <t>163157</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>77082</t>
+          <t>77383</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>97659</t>
+          <t>97521</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>91396</t>
+          <t>92748</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>114528</t>
+          <t>114457</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>174235</t>
+          <t>175741</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>205205</t>
+          <t>206488</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10932,12 +10932,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11010,12 +11010,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -11088,12 +11088,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11123,12 +11123,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11158,12 +11158,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13216</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -11201,12 +11201,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11216,12 +11216,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21831</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11579,12 +11579,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11614,12 +11614,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>770</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -11770,12 +11770,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11805,12 +11805,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -11883,12 +11883,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11898,12 +11898,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11918,12 +11918,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14822</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24491</t>
+          <t>24548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,58%</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -12452,12 +12452,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12537,12 +12537,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -12565,12 +12565,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12635,12 +12635,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -13021,12 +13021,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13091,12 +13091,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13106,12 +13106,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -13134,12 +13134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23322</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13169,12 +13169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13184,12 +13184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13204,12 +13204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22323</t>
+          <t>23144</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36657</t>
+          <t>36441</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13219,12 +13219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28107</t>
+          <t>27930</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13262,12 +13262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13282,12 +13282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17480</t>
+          <t>17554</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13297,12 +13297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38325</t>
+          <t>37887</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>52433</t>
+          <t>52003</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13332,12 +13332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -13816,12 +13816,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14843</t>
+          <t>14637</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13831,12 +13831,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13851,12 +13851,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13866,12 +13866,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13886,12 +13886,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>22121</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -13929,12 +13929,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10945</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18978</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13944,12 +13944,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13964,12 +13964,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21686</t>
+          <t>21389</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13979,12 +13979,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13999,12 +13999,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>27412</t>
+          <t>27983</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>38794</t>
+          <t>39259</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14533,12 +14533,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14548,12 +14548,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14568,12 +14568,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>50,53%</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -14646,12 +14646,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14661,12 +14661,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14681,12 +14681,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14696,12 +14696,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -14881,7 +14881,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15004,12 +15004,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15039,12 +15039,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15067,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15152,12 +15152,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -15180,12 +15180,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>33785</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>49806</t>
+          <t>50075</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>23284</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>38647</t>
+          <t>39727</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15230,12 +15230,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>61172</t>
+          <t>62008</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>83764</t>
+          <t>84867</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15265,12 +15265,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -15293,12 +15293,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>55589</t>
+          <t>55771</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>72590</t>
+          <t>72832</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15308,12 +15308,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15328,12 +15328,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>69772</t>
+          <t>68383</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>87299</t>
+          <t>86068</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15343,12 +15343,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15363,12 +15363,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>130089</t>
+          <t>130909</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>154957</t>
+          <t>154170</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,57%</t>
         </is>
       </c>
     </row>
@@ -15870,12 +15870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -15940,12 +15940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -15955,12 +15955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -15983,12 +15983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -15998,12 +15998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -16018,12 +16018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -16053,12 +16053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10088</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -16096,12 +16096,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>491</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -16111,12 +16111,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -16131,12 +16131,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -16166,12 +16166,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -16209,12 +16209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>18111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -16244,12 +16244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>21624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>31937</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,14%</t>
         </is>
       </c>
     </row>
@@ -16552,12 +16552,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -16567,12 +16567,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -16622,12 +16622,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -16665,12 +16665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16680,12 +16680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16700,12 +16700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>792</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -16715,12 +16715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -16735,12 +16735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -16891,12 +16891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -16906,12 +16906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -16941,12 +16941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -16976,12 +16976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -17239,7 +17239,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -17304,12 +17304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -17319,12 +17319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -17465,7 +17465,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -17495,12 +17495,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -17510,12 +17510,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -17530,12 +17530,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -17545,12 +17545,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -17573,12 +17573,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -17588,12 +17588,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -17608,12 +17608,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -17623,12 +17623,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -17643,12 +17643,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>16696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -17658,12 +17658,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -17956,7 +17956,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -17971,7 +17971,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -18064,12 +18064,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>539</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -18079,12 +18079,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -18114,12 +18114,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -18142,12 +18142,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15705</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -18157,12 +18157,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -18177,12 +18177,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -18192,12 +18192,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -18212,12 +18212,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25497</t>
+          <t>24904</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -18227,12 +18227,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -18255,12 +18255,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19706</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30992</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -18290,12 +18290,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21064</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30600</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -18305,12 +18305,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -18325,12 +18325,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43343</t>
+          <t>44422</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58600</t>
+          <t>58860</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -18340,12 +18340,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -18603,7 +18603,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -18638,7 +18638,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -18751,7 +18751,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18786,7 +18786,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -18801,7 +18801,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -18824,12 +18824,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18839,12 +18839,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -18874,12 +18874,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18894,12 +18894,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16838</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18909,12 +18909,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -18937,12 +18937,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -18952,12 +18952,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -18972,12 +18972,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>11377</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -18987,12 +18987,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -19007,12 +19007,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>24878</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>35723</t>
+          <t>35654</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -19398,7 +19398,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -19483,7 +19483,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -19511,7 +19511,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -19541,12 +19541,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -19556,12 +19556,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -19576,12 +19576,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>534</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19591,12 +19591,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -19654,12 +19654,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -19669,12 +19669,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -19689,12 +19689,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19704,12 +19704,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -19962,12 +19962,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19977,12 +19977,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19997,12 +19997,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -20012,12 +20012,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -20032,12 +20032,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -20047,12 +20047,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -20075,12 +20075,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -20090,12 +20090,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -20110,12 +20110,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -20125,12 +20125,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20145,12 +20145,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>24030</t>
+          <t>24340</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -20160,12 +20160,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -20188,12 +20188,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26017</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -20203,12 +20203,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20223,12 +20223,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>36973</t>
+          <t>36499</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -20238,12 +20238,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20258,12 +20258,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>36752</t>
+          <t>36235</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>58851</t>
+          <t>58380</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -20273,12 +20273,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -20301,12 +20301,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>61697</t>
+          <t>60660</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>77601</t>
+          <t>77465</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20336,12 +20336,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>63552</t>
+          <t>63530</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>83173</t>
+          <t>82688</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -20351,12 +20351,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20371,12 +20371,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>129071</t>
+          <t>129888</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>155241</t>
+          <t>156744</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -20386,12 +20386,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
